--- a/reports/Debug-purgatory-20260104/For The Day (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Day (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -64,21 +64,48 @@
     <t>Village Market Deli</t>
   </si>
   <si>
-    <t>Guest Services</t>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>General Administration</t>
   </si>
   <si>
     <t>account</t>
   </si>
   <si>
+    <t>T103</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
-    <t>T103</t>
-  </si>
-  <si>
     <t>T105</t>
   </si>
   <si>
+    <t>T101</t>
+  </si>
+  <si>
     <t>T100</t>
   </si>
   <si>
@@ -115,7 +142,7 @@
     <t>D5202</t>
   </si>
   <si>
-    <t xml:space="preserve">D5205                    </t>
+    <t>D5205</t>
   </si>
   <si>
     <t>D5206</t>
@@ -130,7 +157,31 @@
     <t>D5209</t>
   </si>
   <si>
-    <t xml:space="preserve">D6720                    </t>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D8010</t>
   </si>
   <si>
     <t>revenue</t>
@@ -496,13 +547,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -510,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -524,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2">
-        <v>69.5000</v>
+        <v>300.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -538,13 +589,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2">
-        <v>300.0000</v>
+        <v>69.50</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -552,13 +603,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2">
-        <v>870.0000</v>
+        <v>870.00</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -566,193 +617,303 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2">
-        <v>132468.3000</v>
+        <v>81948.45</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2">
-        <v>28903.4000</v>
+        <v>132438.30</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2">
-        <v>1120.0000</v>
+        <v>46244.41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2">
-        <v>26053.5000</v>
+        <v>1120.00</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2">
-        <v>1174.9900</v>
+        <v>26353.50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2">
-        <v>10049.7300</v>
+        <v>1174.99</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D11" s="2">
-        <v>2452.2100</v>
+        <v>10049.73</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2">
-        <v>4227.0100</v>
+        <v>2452.21</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2">
-        <v>6252.4000</v>
+        <v>4227.01</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2">
-        <v>12132.9900</v>
+        <v>6252.40</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2">
-        <v>1594.6000</v>
+        <v>12132.99</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D16" s="2">
-        <v>310.0000</v>
+        <v>1594.60</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2">
-        <v>6377.6300</v>
+        <v>310.00</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D18" s="2">
-        <v>14276.0300</v>
+        <v>6377.63</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2">
-        <v>2794.5100</v>
+        <v>14276.03</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2">
-        <v>300.0000</v>
+        <v>2794.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="2">
+        <v>54891.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1145.00</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="2">
+        <v>625.95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1533.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="2">
+        <v>210.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="2">
+        <v>665.41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="2">
+        <v>448.22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="2">
+        <v>408.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2485.95</v>
       </c>
     </row>
   </sheetData>
